--- a/ott_cinema_dataset.xlsx
+++ b/ott_cinema_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9d1c894097c761c/Masaüstü/UNIPD/2-1/BUSINESS^J ECONOMIC AND FINANCIAL DATA/BEFD_Final_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{10E86178-9A90-4768-AB0F-543806C97FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{879D5034-C17C-46BA-BE6A-07DDDFE225BC}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{10E86178-9A90-4768-AB0F-543806C97FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6B2007E-2CCB-4EBB-8F00-7EF9DCECEE48}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58156B1C-79D7-4976-AA10-6C7042AA2D11}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{58156B1C-79D7-4976-AA10-6C7042AA2D11}"/>
   </bookViews>
   <sheets>
     <sheet name="Monthly" sheetId="1" r:id="rId1"/>
@@ -244,116 +244,8 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Zeynep Tutar</author>
-  </authors>
-  <commentList>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{8E5811B0-39DA-4020-B324-250021DE4620}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Zeynep Tutar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-ISTAT
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{F8C72712-78DF-499F-BA3C-9EA95EF5429F}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Zeynep Tutar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-ISTAT
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{67FFADD6-66F7-45E7-9DC7-421506AFE81F}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Zeynep Tutar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-ISTAT</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{EE0C1F84-9D3D-4106-B648-F5368805D78E}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Zeynep Tutar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-https://www.epicentro.iss.it/coronavirus/sars-cov-2-dashboard</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="228">
   <si>
     <t>Time</t>
   </si>
@@ -1033,28 +925,21 @@
     <t>Year</t>
   </si>
   <si>
-    <t>ott_subscriptions</t>
-  </si>
-  <si>
-    <t>ott_spending</t>
-  </si>
-  <si>
-    <t>cinema_avg_ticket_prices</t>
-  </si>
-  <si>
-    <t>households_w_internet</t>
+    <t>ott_subscriptions_M</t>
+  </si>
+  <si>
+    <t>ott_spending_M_EUR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -1164,7 +1049,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1207,12 +1092,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7958,17 +7837,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97207175-89FB-426B-87E6-4F992A448402}">
-  <dimension ref="A1:K19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97207175-89FB-426B-87E6-4F992A448402}">
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.77734375" customWidth="1"/>
-    <col min="2" max="6" width="16.109375" customWidth="1"/>
-    <col min="7" max="7" width="15.77734375" customWidth="1"/>
-    <col min="8" max="11" width="16.109375" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>225</v>
       </c>
@@ -7981,33 +7860,12 @@
       <c r="D1" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="13">
         <v>2006</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="15">
         <v>0</v>
       </c>
       <c r="C2" s="14">
@@ -8016,33 +7874,12 @@
       <c r="D2" s="15">
         <v>106200111</v>
       </c>
-      <c r="E2" s="15">
-        <v>1220229</v>
-      </c>
-      <c r="F2" s="14">
-        <v>678812668.38</v>
-      </c>
-      <c r="G2" s="14">
-        <v>5.73</v>
-      </c>
-      <c r="H2" s="16">
-        <v>1.8</v>
-      </c>
-      <c r="I2" s="16">
-        <v>1.5</v>
-      </c>
-      <c r="J2" s="16">
-        <v>35.6</v>
-      </c>
-      <c r="K2" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="13">
         <v>2007</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="15">
         <v>0</v>
       </c>
       <c r="C3" s="14">
@@ -8051,588 +7888,232 @@
       <c r="D3" s="15">
         <v>117372430</v>
       </c>
-      <c r="E3" s="15">
-        <v>1266082</v>
-      </c>
-      <c r="F3" s="14">
-        <v>743362280.22000015</v>
-      </c>
-      <c r="G3" s="14">
-        <v>5.7512089443961543</v>
-      </c>
-      <c r="H3" s="16">
-        <v>2.6</v>
-      </c>
-      <c r="I3" s="16">
-        <v>0.8</v>
-      </c>
-      <c r="J3" s="16">
-        <v>38.799999999999997</v>
-      </c>
-      <c r="K3" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="13">
         <v>2008</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="15">
         <v>0</v>
       </c>
       <c r="C4" s="14">
-        <v>600000</v>
+        <v>0.6</v>
       </c>
       <c r="D4" s="15">
         <v>111810894</v>
       </c>
-      <c r="E4" s="15">
-        <v>1513907</v>
-      </c>
-      <c r="F4" s="14">
-        <v>698611949.02999997</v>
-      </c>
-      <c r="G4" s="14">
-        <v>5.73</v>
-      </c>
-      <c r="H4" s="16">
-        <v>2.1</v>
-      </c>
-      <c r="I4" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="J4" s="16">
-        <v>42</v>
-      </c>
-      <c r="K4" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="13">
         <v>2009</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="15">
         <v>0</v>
       </c>
       <c r="C5" s="14">
-        <v>700000</v>
+        <v>0.7</v>
       </c>
       <c r="D5" s="15">
         <v>111474620</v>
       </c>
-      <c r="E5" s="15">
-        <v>1785945</v>
-      </c>
-      <c r="F5" s="14">
-        <v>743347501.10000002</v>
-      </c>
-      <c r="G5" s="14">
-        <v>6.079614003563055</v>
-      </c>
-      <c r="H5" s="16">
-        <v>1.2</v>
-      </c>
-      <c r="I5" s="16">
-        <v>0.8</v>
-      </c>
-      <c r="J5" s="16">
-        <v>47.3</v>
-      </c>
-      <c r="K5" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="13">
         <v>2010</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="15">
         <v>0</v>
       </c>
       <c r="C6" s="14">
-        <v>1400000</v>
+        <v>1.4</v>
       </c>
       <c r="D6" s="15">
         <v>122719372</v>
       </c>
-      <c r="E6" s="15">
-        <v>2558481</v>
-      </c>
-      <c r="F6" s="14">
-        <v>849841907.92000008</v>
-      </c>
-      <c r="G6" s="14">
-        <v>6.4086472707702287</v>
-      </c>
-      <c r="H6" s="16">
-        <v>1.9</v>
-      </c>
-      <c r="I6" s="16">
-        <v>0.8</v>
-      </c>
-      <c r="J6" s="16">
-        <v>52.4</v>
-      </c>
-      <c r="K6" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
         <v>2011</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="15">
         <v>0</v>
       </c>
       <c r="C7" s="14">
-        <v>9500000</v>
+        <v>9.5</v>
       </c>
       <c r="D7" s="15">
         <v>114418580</v>
       </c>
-      <c r="E7" s="15">
-        <v>2975624</v>
-      </c>
-      <c r="F7" s="14">
-        <v>751456158.63999975</v>
-      </c>
-      <c r="G7" s="14">
-        <v>6.2184260571561385</v>
-      </c>
-      <c r="H7" s="16">
-        <v>3.3</v>
-      </c>
-      <c r="I7" s="16">
-        <v>-0.2</v>
-      </c>
-      <c r="J7" s="16">
-        <v>54.5</v>
-      </c>
-      <c r="K7" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
         <v>2012</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="15">
         <v>0</v>
       </c>
       <c r="C8" s="14">
-        <v>21900000</v>
+        <v>21.9</v>
       </c>
       <c r="D8" s="15">
         <v>102633108</v>
       </c>
-      <c r="E8" s="15">
-        <v>2983555</v>
-      </c>
-      <c r="F8" s="14">
-        <v>716822785.71000028</v>
-      </c>
-      <c r="G8" s="14">
-        <v>6.361737315532106</v>
-      </c>
-      <c r="H8" s="16">
-        <v>2.4</v>
-      </c>
-      <c r="I8" s="16">
-        <v>-0.4</v>
-      </c>
-      <c r="J8" s="16">
-        <v>55.5</v>
-      </c>
-      <c r="K8" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
         <v>2013</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="15">
         <v>0</v>
       </c>
       <c r="C9" s="14">
-        <v>21100000</v>
+        <v>21.1</v>
       </c>
       <c r="D9" s="15">
         <v>106124433</v>
       </c>
-      <c r="E9" s="15">
-        <v>3014642</v>
-      </c>
-      <c r="F9" s="14">
-        <v>732299026.82000005</v>
-      </c>
-      <c r="G9" s="14">
-        <v>6.0841684923130002</v>
-      </c>
-      <c r="H9" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="I9" s="16">
-        <v>1</v>
-      </c>
-      <c r="J9" s="16">
-        <v>60.6</v>
-      </c>
-      <c r="K9" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>2014</v>
       </c>
-      <c r="B10" s="4">
-        <v>300000</v>
+      <c r="B10" s="15">
+        <v>0.3</v>
       </c>
       <c r="C10" s="14">
-        <v>39000000</v>
+        <v>39</v>
       </c>
       <c r="D10" s="15">
         <v>98305277</v>
       </c>
-      <c r="E10" s="15">
-        <v>3016007</v>
-      </c>
-      <c r="F10" s="14">
-        <v>690685660.04000008</v>
-      </c>
-      <c r="G10" s="14">
-        <v>6.1074098285059115</v>
-      </c>
-      <c r="H10" s="16">
-        <v>-0.1</v>
-      </c>
-      <c r="I10" s="16">
-        <v>0</v>
-      </c>
-      <c r="J10" s="16">
-        <v>64</v>
-      </c>
-      <c r="K10" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <v>2015</v>
       </c>
-      <c r="B11" s="4">
-        <v>800000</v>
+      <c r="B11" s="15">
+        <v>0.8</v>
       </c>
       <c r="C11" s="14">
-        <v>64099999.999999993</v>
+        <v>64.099999999999994</v>
       </c>
       <c r="D11" s="15">
         <v>107016526</v>
       </c>
-      <c r="E11" s="15">
-        <v>3096351</v>
-      </c>
-      <c r="F11" s="14">
-        <v>770232824.08000004</v>
-      </c>
-      <c r="G11" s="14">
-        <v>6.2234769107017165</v>
-      </c>
-      <c r="H11" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="I11" s="16">
-        <v>0.7</v>
-      </c>
-      <c r="J11" s="16">
-        <v>66.2</v>
-      </c>
-      <c r="K11" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <v>2016</v>
       </c>
-      <c r="B12" s="4">
-        <v>1300000</v>
+      <c r="B12" s="15">
+        <v>1.3</v>
       </c>
       <c r="C12" s="14">
-        <v>122000000</v>
+        <v>122</v>
       </c>
       <c r="D12" s="15">
         <v>114228577</v>
       </c>
-      <c r="E12" s="15">
-        <v>3226957</v>
-      </c>
-      <c r="F12" s="14">
-        <v>810304243.82000482</v>
-      </c>
-      <c r="G12" s="14">
-        <v>6.1060024199411105</v>
-      </c>
-      <c r="H12" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="I12" s="16">
-        <v>0.4</v>
-      </c>
-      <c r="J12" s="16">
-        <v>69.2</v>
-      </c>
-      <c r="K12" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
         <v>2017</v>
       </c>
-      <c r="B13" s="4">
-        <v>3400000</v>
+      <c r="B13" s="15">
+        <v>3.4</v>
       </c>
       <c r="C13" s="14">
-        <v>202700000</v>
+        <v>202.7</v>
       </c>
       <c r="D13" s="15">
         <v>100163629</v>
       </c>
-      <c r="E13" s="15">
-        <v>3142790</v>
-      </c>
-      <c r="F13" s="14">
-        <v>732889604.68000007</v>
-      </c>
-      <c r="G13" s="14">
-        <v>6.2177305716072206</v>
-      </c>
-      <c r="H13" s="16">
-        <v>0.8</v>
-      </c>
-      <c r="I13" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="J13" s="16">
-        <v>71.7</v>
-      </c>
-      <c r="K13" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>2018</v>
       </c>
-      <c r="B14" s="4">
-        <v>5600000</v>
+      <c r="B14" s="15">
+        <v>5.6</v>
       </c>
       <c r="C14" s="14">
-        <v>342900000</v>
+        <v>342.9</v>
       </c>
       <c r="D14" s="15">
         <v>92197575</v>
       </c>
-      <c r="E14" s="15">
-        <v>3164690</v>
-      </c>
-      <c r="F14" s="14">
-        <v>682410753.0799998</v>
-      </c>
-      <c r="G14" s="14">
-        <v>6.4339038284732162</v>
-      </c>
-      <c r="H14" s="16">
-        <v>1</v>
-      </c>
-      <c r="I14" s="16">
-        <v>-0.3</v>
-      </c>
-      <c r="J14" s="16">
-        <v>75.099999999999994</v>
-      </c>
-      <c r="K14" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
         <v>2019</v>
       </c>
-      <c r="B15" s="4">
-        <v>8500000</v>
+      <c r="B15" s="15">
+        <v>8.5</v>
       </c>
       <c r="C15" s="14">
-        <v>473700000</v>
+        <v>473.7</v>
       </c>
       <c r="D15" s="15">
         <v>104804587</v>
       </c>
-      <c r="E15" s="15">
-        <v>3245345</v>
-      </c>
-      <c r="F15" s="14">
-        <v>791989946.06000006</v>
-      </c>
-      <c r="G15" s="14">
-        <v>6.5338135009692211</v>
-      </c>
-      <c r="H15" s="16">
-        <v>0.4</v>
-      </c>
-      <c r="I15" s="16">
-        <v>-0.1</v>
-      </c>
-      <c r="J15" s="16">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="K15" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
         <v>2020</v>
       </c>
-      <c r="B16" s="4">
-        <v>15300000</v>
+      <c r="B16" s="15">
+        <v>15.3</v>
       </c>
       <c r="C16" s="14">
-        <v>767400000</v>
+        <v>767.4</v>
       </c>
       <c r="D16" s="15">
         <v>30370867</v>
       </c>
-      <c r="E16" s="15">
-        <v>996009</v>
-      </c>
-      <c r="F16" s="14">
-        <v>212155149.66000006</v>
-      </c>
-      <c r="G16" s="14">
-        <v>6.4227757502028213</v>
-      </c>
-      <c r="H16" s="16">
-        <v>-0.1</v>
-      </c>
-      <c r="I16" s="16">
-        <v>0.9</v>
-      </c>
-      <c r="J16" s="16">
-        <v>79</v>
-      </c>
-      <c r="K16" s="17">
-        <v>2182299</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
         <v>2021</v>
       </c>
-      <c r="B17" s="4">
-        <v>20300000</v>
+      <c r="B17" s="15">
+        <v>20.3</v>
       </c>
       <c r="C17" s="14">
-        <v>1055599999.9999999</v>
+        <v>1055.5999999999999</v>
       </c>
       <c r="D17" s="15">
         <v>26806033</v>
       </c>
-      <c r="E17" s="15">
-        <v>1350766</v>
-      </c>
-      <c r="F17" s="14">
-        <v>185916560.14999998</v>
-      </c>
-      <c r="G17" s="14">
-        <v>6.9186011183487937</v>
-      </c>
-      <c r="H17" s="16">
-        <v>3.8</v>
-      </c>
-      <c r="I17" s="16">
-        <v>-0.2</v>
-      </c>
-      <c r="J17" s="16">
-        <v>81.5</v>
-      </c>
-      <c r="K17" s="17">
-        <v>4285023</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
         <v>2022</v>
       </c>
-      <c r="B18" s="4">
-        <v>21500000</v>
+      <c r="B18" s="15">
+        <v>21.5</v>
       </c>
       <c r="C18" s="14">
-        <v>1096000000</v>
+        <v>1096</v>
       </c>
       <c r="D18" s="15">
         <v>47651620</v>
       </c>
-      <c r="E18" s="15">
-        <v>2255029</v>
-      </c>
-      <c r="F18" s="14">
-        <v>333035442.10000008</v>
-      </c>
-      <c r="G18" s="14">
-        <v>6.9889636931546093</v>
-      </c>
-      <c r="H18" s="16">
-        <v>11</v>
-      </c>
-      <c r="I18" s="16">
-        <v>3.4</v>
-      </c>
-      <c r="J18" s="16">
-        <v>83.1</v>
-      </c>
-      <c r="K18" s="17">
-        <v>18972014</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
         <v>2023</v>
       </c>
-      <c r="B19" s="4">
-        <v>22800000</v>
+      <c r="B19" s="15">
+        <v>22.8</v>
       </c>
       <c r="C19" s="14">
-        <v>1271000000</v>
+        <v>1271</v>
       </c>
       <c r="D19" s="15">
         <v>74063450</v>
       </c>
-      <c r="E19" s="15">
-        <v>2579112</v>
-      </c>
-      <c r="F19" s="14">
-        <v>530531050.17000002</v>
-      </c>
-      <c r="G19" s="14">
-        <v>7.1631965587614408</v>
-      </c>
-      <c r="H19" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="I19" s="16">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J19" s="16"/>
-      <c r="K19" s="17">
-        <v>1442406</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ott_cinema_dataset.xlsx
+++ b/ott_cinema_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9d1c894097c761c/Masaüstü/UNIPD/2-1/BUSINESS^J ECONOMIC AND FINANCIAL DATA/BEFD_Final_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{10E86178-9A90-4768-AB0F-543806C97FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6B2007E-2CCB-4EBB-8F00-7EF9DCECEE48}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{10E86178-9A90-4768-AB0F-543806C97FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{329F12DF-F898-4250-A2A1-59C3EB265EAA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{58156B1C-79D7-4976-AA10-6C7042AA2D11}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58156B1C-79D7-4976-AA10-6C7042AA2D11}"/>
   </bookViews>
   <sheets>
     <sheet name="Monthly" sheetId="1" r:id="rId1"/>

--- a/ott_cinema_dataset.xlsx
+++ b/ott_cinema_dataset.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9d1c894097c761c/Masaüstü/UNIPD/2-1/BUSINESS^J ECONOMIC AND FINANCIAL DATA/BEFD_Final_Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9d1c894097c761c/Masaüstü/UNIPD/2-2/BUSINESS^J ECONOMIC AND FINANCIAL DATA/BEFD_Final_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="72" documentId="8_{10E86178-9A90-4768-AB0F-543806C97FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{329F12DF-F898-4250-A2A1-59C3EB265EAA}"/>
@@ -1112,10 +1112,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
